--- a/diseases/d178/2005-2009.xlsx
+++ b/diseases/d178/2005-2009.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,84 +760,95 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05257408987185788</v>
+        <v>0.1633776737257227</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -864,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -899,93 +910,179 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2005-02-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.03504939324790526</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>53</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1047,25 +1144,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2005-03-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04381174155988157</v>
+        <v>0.05257408987185788</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1195,25 +1292,25 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2005-04-01</t>
+          <t>2005-02-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02190587077994079</v>
+        <v>0.03504939324790526</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1343,25 +1440,25 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2005-05-01</t>
+          <t>2005-03-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03943056740389342</v>
+        <v>0.04381174155988157</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1491,25 +1588,25 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>2005-04-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01752469662395263</v>
+        <v>0.02190587077994079</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1639,25 +1736,25 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-05-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01752469662395263</v>
+        <v>0.03943056740389342</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1787,25 +1884,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0306682190919171</v>
+        <v>0.01752469662395263</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1935,25 +2032,25 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02190587077994079</v>
+        <v>0.01752469662395263</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2083,25 +2180,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02190587077994079</v>
+        <v>0.0306682190919171</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2231,25 +2328,25 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2005-11-01</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01752469662395263</v>
+        <v>0.02190587077994079</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2379,25 +2476,25 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-10-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.004381174155988157</v>
+        <v>0.02190587077994079</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2527,12 +2624,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2005-11-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2545,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01745609377832524</v>
+        <v>0.01752469662395263</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2675,25 +2772,25 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2005-12-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.02182011722290655</v>
+        <v>0.004381174155988157</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2793,12 +2890,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2823,93 +2920,104 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01309207033374393</v>
+        <v>0.119050631653652</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2936,17 +3044,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2971,93 +3079,179 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.01309207033374393</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3119,25 +3313,25 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.03927621100123179</v>
+        <v>0.01745609377832524</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3267,25 +3461,25 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.03054816411206917</v>
+        <v>0.02182011722290655</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3415,25 +3609,25 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.01745609377832524</v>
+        <v>0.01309207033374393</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3563,25 +3757,25 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0916444923362075</v>
+        <v>0.01309207033374393</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -3711,25 +3905,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06109632822413834</v>
+        <v>0.03927621100123179</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3829,12 +4023,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3859,25 +4053,25 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.02598748188301263</v>
+        <v>0.03054816411206917</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -3910,42 +4104,42 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4007,25 +4201,25 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.05215821115417255</v>
+        <v>0.01745609377832524</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4125,12 +4319,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4155,25 +4349,25 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="O25" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.03394283347985323</v>
+        <v>0.0916444923362075</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -4206,42 +4400,42 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4303,25 +4497,25 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02173258798090523</v>
+        <v>0.06109632822413834</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4451,25 +4645,25 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="O27" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02810890897550346</v>
+        <v>0.02598748188301263</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4569,12 +4763,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4599,93 +4793,104 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N28" t="n">
+        <v>50</v>
+      </c>
+      <c r="O28" t="n">
+        <v>50</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1510931369372361</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
         <v>1</v>
       </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.004346517596181046</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4917,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4747,93 +4952,179 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="O29" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.03765533089171218</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4895,25 +5186,25 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.02607910557708627</v>
+        <v>0.05215821115417255</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -5043,25 +5334,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="O31" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.02916962252174887</v>
+        <v>0.03394283347985323</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5191,25 +5482,25 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01738607038472418</v>
+        <v>0.02173258798090523</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -5339,25 +5630,25 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="O33" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.04136782830357113</v>
+        <v>0.02810890897550346</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -5487,25 +5778,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01738607038472418</v>
+        <v>0.004346517596181046</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5635,25 +5926,25 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="O35" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.02757855220238075</v>
+        <v>0.03765533089171218</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -5783,25 +6074,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01303955278854314</v>
+        <v>0.02607910557708627</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -5931,25 +6222,25 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="O37" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.03394283347985323</v>
+        <v>0.02916962252174887</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6079,25 +6370,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.008693035192362092</v>
+        <v>0.01738607038472418</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6227,25 +6518,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="O39" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.02704819542925804</v>
+        <v>0.04136782830357113</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6375,25 +6666,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.02173258798090523</v>
+        <v>0.01738607038472418</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6523,25 +6814,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="O41" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.03500354702609864</v>
+        <v>0.02757855220238075</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6671,25 +6962,25 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.02607910557708627</v>
+        <v>0.01303955278854314</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -6819,25 +7110,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="O43" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02174462769803098</v>
+        <v>0.03394283347985323</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -6937,12 +7228,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6967,25 +7258,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02227498447115368</v>
+        <v>0.008693035192362092</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7018,42 +7309,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7376,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7115,25 +7406,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.03042562317326732</v>
+        <v>0.02704819542925804</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7166,42 +7457,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7524,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7263,25 +7554,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.02416381365788284</v>
+        <v>0.02173258798090523</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7314,42 +7605,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7672,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7411,25 +7702,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.02598950829539623</v>
+        <v>0.03500354702609864</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7462,42 +7753,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7820,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7559,25 +7850,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.02679031514243532</v>
+        <v>0.02607910557708627</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -7610,42 +7901,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7677,12 +7968,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7707,25 +7998,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02598950829539623</v>
+        <v>0.02174462769803098</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -7758,42 +8049,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -7855,25 +8146,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="O50" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.02784091573625631</v>
+        <v>0.02227498447115368</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -8003,12 +8294,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8021,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0303210930112956</v>
+        <v>0.03042562317326732</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8151,25 +8442,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="O52" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.03256861840845078</v>
+        <v>0.02416381365788284</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8269,12 +8560,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8299,93 +8590,104 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R53" t="n">
-        <v>0.04331584715899372</v>
+        <v>0.1255639728261625</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8412,17 +8714,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8447,93 +8749,179 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="O54" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.02731561543934581</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8595,25 +8983,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.03898426244309434</v>
+        <v>0.02598950829539623</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8743,25 +9131,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="O56" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.03572042018991376</v>
+        <v>0.02679031514243532</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -8891,25 +9279,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.04331584715899372</v>
+        <v>0.02598950829539623</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -9039,25 +9427,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O58" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0304674172208088</v>
+        <v>0.02784091573625631</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9187,12 +9575,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9335,25 +9723,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O60" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.03572042018991376</v>
+        <v>0.03256861840845078</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9483,25 +9871,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.02165792357949686</v>
+        <v>0.04331584715899372</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9631,25 +10019,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O62" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.02679031514243532</v>
+        <v>0.02731561543934581</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -9779,25 +10167,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.02165792357949686</v>
+        <v>0.03898426244309434</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -9927,25 +10315,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="O64" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.02153731217333036</v>
+        <v>0.03572042018991376</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10075,25 +10463,25 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.02598950829539623</v>
+        <v>0.04331584715899372</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10223,25 +10611,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="O66" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.02153731217333036</v>
+        <v>0.0304674172208088</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10371,25 +10759,25 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.01299475414769812</v>
+        <v>0.0303210930112956</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -10519,25 +10907,25 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="O68" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01733490979804638</v>
+        <v>0.03572042018991376</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -10667,25 +11055,25 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01732633886359749</v>
+        <v>0.02165792357949686</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -10815,25 +11203,25 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O70" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.02342774447976547</v>
+        <v>0.02679031514243532</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -10963,12 +11351,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -10981,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.02158488205221806</v>
+        <v>0.02165792357949686</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -11111,25 +11499,25 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O72" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01561849631984365</v>
+        <v>0.02153731217333036</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -11259,25 +11647,25 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.008633952820887223</v>
+        <v>0.02598950829539623</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -11407,25 +11795,25 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="O74" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.02707206028772899</v>
+        <v>0.02153731217333036</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -11555,25 +11943,25 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.008633952820887223</v>
+        <v>0.01299475414769812</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -11703,25 +12091,25 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O76" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.02394836102376026</v>
+        <v>0.01733490979804638</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -11851,12 +12239,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -11869,7 +12257,7 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.01726790564177445</v>
+        <v>0.01732633886359749</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -11999,25 +12387,25 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O78" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.02394836102376026</v>
+        <v>0.02342774447976547</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -12117,12 +12505,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12147,93 +12535,104 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="O79" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02158488205221806</v>
+        <v>0.1744201317726358</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12260,17 +12659,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12295,93 +12694,179 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O80" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.03175760918368208</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN80" t="b">
+        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12443,25 +12928,25 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0.02590185846266167</v>
+        <v>0.02158488205221806</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -12591,25 +13076,25 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="O82" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.01874219558381238</v>
+        <v>0.01561849631984365</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -12739,25 +13224,25 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.02158488205221806</v>
+        <v>0.008633952820887223</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -12887,25 +13372,25 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="O84" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.03227822572767687</v>
+        <v>0.02707206028772899</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -13035,25 +13520,25 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01726790564177445</v>
+        <v>0.008633952820887223</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -13183,12 +13668,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13331,12 +13816,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13479,25 +13964,25 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O88" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01822157903981759</v>
+        <v>0.02394836102376026</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -13627,25 +14112,25 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.01295092923133083</v>
+        <v>0.02158488205221806</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -13775,25 +14260,25 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="O90" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.02186589484778111</v>
+        <v>0.03175760918368208</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -13893,12 +14378,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13923,25 +14408,25 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="O91" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.02134527830378632</v>
+        <v>0.02590185846266167</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -13974,42 +14459,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14041,12 +14526,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14071,25 +14556,25 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O92" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.02158488205221806</v>
+        <v>0.01874219558381238</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -14122,40 +14607,1520 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.02158488205221806</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW92" t="inlineStr">
+      <c r="AW93" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
+      <c r="AX93" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY92" t="inlineStr">
+      <c r="AY93" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA92" t="inlineStr">
+      <c r="BA93" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB92" t="inlineStr">
+      <c r="BB93" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC92" t="inlineStr">
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>62</v>
+      </c>
+      <c r="O94" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.03227822572767687</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>4</v>
+      </c>
+      <c r="O95" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.01726790564177445</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>46</v>
+      </c>
+      <c r="O96" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.02394836102376026</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.01726790564177445</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>35</v>
+      </c>
+      <c r="O98" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.01822157903981759</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.01295092923133083</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>42</v>
+      </c>
+      <c r="O100" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.02186589484778111</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>41</v>
+      </c>
+      <c r="O101" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.02134527830378632</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>5</v>
+      </c>
+      <c r="O102" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.02158488205221806</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -14277,7 +16242,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -14287,7 +16252,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -14307,7 +16272,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -14317,7 +16282,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14339,7 +16304,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2174</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="16">
